--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472392</v>
       </c>
       <c r="B2" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472392</v>
       </c>
       <c r="B2" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472392</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129472390</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472391</v>
       </c>
       <c r="B4" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48717-2024 artfynd.xlsx
+++ b/artfynd/A 48717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129472392</v>
+        <v>129472390</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690207</v>
+        <v>690226</v>
       </c>
       <c r="R2" t="n">
-        <v>6615598</v>
+        <v>6615607</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472390</v>
+        <v>109473518</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrskog O Mårdsjön, Upl</t>
+          <t>Hoven, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690226</v>
+        <v>690267</v>
       </c>
       <c r="R3" t="n">
-        <v>6615607</v>
+        <v>6615517</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,56 +857,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>David Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>David Falk, David Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472391</v>
+        <v>109473519</v>
       </c>
       <c r="B4" t="n">
-        <v>91619</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog O Mårdsjön, Upl</t>
+          <t>Hoven, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690207</v>
+        <v>690243</v>
       </c>
       <c r="R4" t="n">
-        <v>6615601</v>
+        <v>6615619</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -930,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -950,15 +958,116 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>David Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Falk, David Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129472392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog O Mårdsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>690207</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6615598</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
